--- a/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
@@ -10603,7 +10603,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>YEAR</t>
   </si>
@@ -138,6 +138,18 @@
     <t>NBR_TP</t>
   </si>
   <si>
+    <t>AC_CRITIQUE</t>
+  </si>
+  <si>
+    <t>FH_DAY</t>
+  </si>
+  <si>
+    <t>FH_TK</t>
+  </si>
+  <si>
+    <t>TK_DAY</t>
+  </si>
+  <si>
     <t>MTN_STATIONS</t>
   </si>
   <si>
@@ -160,9 +172,6 @@
   </si>
   <si>
     <t>T_7</t>
-  </si>
-  <si>
-    <t>MOM</t>
   </si>
   <si>
     <t>TAIL_NUMBER</t>
@@ -202,18 +211,6 @@
   </si>
   <si>
     <t>N128</t>
-  </si>
-  <si>
-    <t>AC_CRITIQUE</t>
-  </si>
-  <si>
-    <t>FH_DAY</t>
-  </si>
-  <si>
-    <t>FH_TK</t>
-  </si>
-  <si>
-    <t>TK_DAY</t>
   </si>
 </sst>
 </file>
@@ -9828,16 +9825,16 @@
         <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -9879,33 +9876,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9913,25 +9910,25 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9939,48 +9936,48 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9988,495 +9985,53 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>3</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="H19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23">
         <v>1</v>
       </c>
     </row>
@@ -10492,24 +10047,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -10526,7 +10081,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -10543,7 +10098,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -10560,7 +10115,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -10577,7 +10132,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -10594,7 +10149,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -10611,7 +10166,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -10628,7 +10183,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_5/354FL_8A_22.xlsx
@@ -9848,16 +9848,16 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>78.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>479</v>
@@ -9928,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9945,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9991,22 +9991,22 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -10073,10 +10073,10 @@
         <v>5330</v>
       </c>
       <c r="D2">
-        <v>45.0</v>
+        <v>70.0</v>
       </c>
       <c r="E2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10090,10 +10090,10 @@
         <v>5275</v>
       </c>
       <c r="D3">
-        <v>44.0</v>
+        <v>69.0</v>
       </c>
       <c r="E3">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10107,10 +10107,10 @@
         <v>4765</v>
       </c>
       <c r="D4">
-        <v>40.0</v>
+        <v>62.0</v>
       </c>
       <c r="E4">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10124,10 +10124,10 @@
         <v>4415</v>
       </c>
       <c r="D5">
-        <v>37.0</v>
+        <v>58.0</v>
       </c>
       <c r="E5">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10141,7 +10141,7 @@
         <v>3755</v>
       </c>
       <c r="D6">
-        <v>32.0</v>
+        <v>49.0</v>
       </c>
       <c r="E6">
         <v>7.0</v>
